--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>127020102</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127020116</v>
       </c>
       <c r="B8" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>127020089</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,34 +1545,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R10" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,13 +1615,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,42 +1655,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R11" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1717,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020088</v>
+        <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721480</v>
+        <v>721477</v>
       </c>
       <c r="R12" t="n">
-        <v>7215986</v>
+        <v>7215978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020075</v>
+        <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721477</v>
+        <v>721480</v>
       </c>
       <c r="R14" t="n">
-        <v>7215978</v>
+        <v>7215986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>127020063</v>
       </c>
       <c r="B15" t="n">
-        <v>92547</v>
+        <v>92621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127020115</v>
       </c>
       <c r="B17" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127020114</v>
       </c>
       <c r="B18" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,34 +2432,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R19" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,42 +2542,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R20" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,11 +2602,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,45 +2725,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R22" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,6 +2804,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,53 +2835,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R23" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,11 +2906,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>82852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R24" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>82792</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R25" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>127020102</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127020116</v>
       </c>
       <c r="B8" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>127020089</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>127020074</v>
       </c>
       <c r="B11" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B15" t="n">
-        <v>92621</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R15" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>92627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R16" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>127020115</v>
       </c>
       <c r="B17" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127020114</v>
       </c>
       <c r="B18" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B24" t="n">
-        <v>82852</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R24" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>82855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R25" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>92627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R15" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>92627</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R16" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,42 +2432,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R19" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,34 +2529,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R20" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,6 +2597,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>82855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R24" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>82855</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R25" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,42 +1545,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R10" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,17 +1607,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,34 +1643,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R11" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,13 +1713,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020075</v>
+        <v>127020088</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721477</v>
+        <v>721480</v>
       </c>
       <c r="R12" t="n">
-        <v>7215978</v>
+        <v>7215986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020066</v>
+        <v>127020075</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721461</v>
+        <v>721477</v>
       </c>
       <c r="R13" t="n">
-        <v>7216007</v>
+        <v>7215978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020088</v>
+        <v>127020066</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721480</v>
+        <v>721461</v>
       </c>
       <c r="R14" t="n">
-        <v>7215986</v>
+        <v>7216007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B10" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,34 +1545,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R10" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,13 +1615,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,42 +1655,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R11" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1717,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020088</v>
+        <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721480</v>
+        <v>721477</v>
       </c>
       <c r="R12" t="n">
-        <v>7215986</v>
+        <v>7215978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020075</v>
+        <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721477</v>
+        <v>721461</v>
       </c>
       <c r="R13" t="n">
-        <v>7215978</v>
+        <v>7216007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020066</v>
+        <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721461</v>
+        <v>721480</v>
       </c>
       <c r="R14" t="n">
-        <v>7216007</v>
+        <v>7215986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B15" t="n">
-        <v>92627</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R15" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>92628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R16" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020075</v>
+        <v>127020088</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721477</v>
+        <v>721480</v>
       </c>
       <c r="R12" t="n">
-        <v>7215978</v>
+        <v>7215986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020066</v>
+        <v>127020075</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721461</v>
+        <v>721477</v>
       </c>
       <c r="R13" t="n">
-        <v>7216007</v>
+        <v>7215978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020088</v>
+        <v>127020066</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721480</v>
+        <v>721461</v>
       </c>
       <c r="R14" t="n">
-        <v>7215986</v>
+        <v>7216007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R15" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>92628</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R16" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020088</v>
+        <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721480</v>
+        <v>721477</v>
       </c>
       <c r="R12" t="n">
-        <v>7215986</v>
+        <v>7215978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020075</v>
+        <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721477</v>
+        <v>721461</v>
       </c>
       <c r="R13" t="n">
-        <v>7215978</v>
+        <v>7216007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020066</v>
+        <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721461</v>
+        <v>721480</v>
       </c>
       <c r="R14" t="n">
-        <v>7216007</v>
+        <v>7215986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,34 +2432,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R19" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,42 +2542,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R20" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,11 +2602,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B24" t="n">
-        <v>82855</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R24" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>82855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R25" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,42 +1545,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R10" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,17 +1607,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,34 +1643,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R11" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,13 +1713,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020075</v>
+        <v>127020088</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721477</v>
+        <v>721480</v>
       </c>
       <c r="R12" t="n">
-        <v>7215978</v>
+        <v>7215986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020066</v>
+        <v>127020075</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721461</v>
+        <v>721477</v>
       </c>
       <c r="R13" t="n">
-        <v>7216007</v>
+        <v>7215978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020088</v>
+        <v>127020066</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721480</v>
+        <v>721461</v>
       </c>
       <c r="R14" t="n">
-        <v>7215986</v>
+        <v>7216007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,42 +2432,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R19" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,34 +2529,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R20" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,6 +2597,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,34 +2432,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R19" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,42 +2542,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R20" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,11 +2602,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,53 +2725,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B22" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R22" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,11 +2796,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,45 +2822,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R23" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,6 +2901,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127020041</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127020039</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>127020102</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127020116</v>
       </c>
       <c r="B8" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>127020089</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B10" t="n">
-        <v>78773</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,34 +1545,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R10" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,13 +1615,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,42 +1655,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R11" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1717,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020088</v>
+        <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721480</v>
+        <v>721477</v>
       </c>
       <c r="R12" t="n">
-        <v>7215986</v>
+        <v>7215978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020075</v>
+        <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721477</v>
+        <v>721461</v>
       </c>
       <c r="R13" t="n">
-        <v>7215978</v>
+        <v>7216007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020066</v>
+        <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721461</v>
+        <v>721480</v>
       </c>
       <c r="R14" t="n">
-        <v>7216007</v>
+        <v>7215986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>127020063</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127020115</v>
       </c>
       <c r="B17" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127020114</v>
       </c>
       <c r="B18" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,45 +2725,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>56853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R22" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,6 +2804,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,53 +2835,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R23" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,11 +2906,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>82859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R24" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>82855</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R25" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,42 +2432,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R19" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,34 +2529,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R20" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,6 +2597,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,53 +2725,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B22" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R22" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,11 +2796,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,45 +2822,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R23" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,6 +2901,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,42 +1545,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R10" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,17 +1607,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,34 +1643,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R11" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,13 +1713,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1939,7 +1939,7 @@
         <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,34 +2432,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R19" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,42 +2542,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R20" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,11 +2602,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,45 +2725,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R22" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,6 +2804,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,53 +2835,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R23" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,11 +2906,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -2725,53 +2725,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B22" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R22" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,11 +2796,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,45 +2822,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>56853</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R23" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,6 +2901,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B24" t="n">
-        <v>82859</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R24" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>82859</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R25" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>127020041</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127020039</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>127020102</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127020116</v>
       </c>
       <c r="B8" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>127020089</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127020074</v>
+        <v>127020043</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,34 +1545,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721639</v>
+        <v>721557</v>
       </c>
       <c r="R10" t="n">
-        <v>7216013</v>
+        <v>7215852</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,13 +1615,17 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127020043</v>
+        <v>127020074</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,42 +1655,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721557</v>
+        <v>721639</v>
       </c>
       <c r="R11" t="n">
-        <v>7215852</v>
+        <v>7216013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,17 +1717,13 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B15" t="n">
-        <v>92632</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R15" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>92634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R16" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>127020115</v>
       </c>
       <c r="B17" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>127020114</v>
       </c>
       <c r="B18" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>127020040</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127020103</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,45 +2725,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R22" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,6 +2804,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,53 +2835,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B23" t="n">
-        <v>56853</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R23" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2901,11 +2906,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>82861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R24" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B25" t="n">
-        <v>82859</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R25" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>92634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R15" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B16" t="n">
-        <v>92634</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R16" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020075</v>
+        <v>127020088</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721477</v>
+        <v>721480</v>
       </c>
       <c r="R12" t="n">
-        <v>7215978</v>
+        <v>7215986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020066</v>
+        <v>127020075</v>
       </c>
       <c r="B13" t="n">
-        <v>80151</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721461</v>
+        <v>721477</v>
       </c>
       <c r="R13" t="n">
-        <v>7216007</v>
+        <v>7215978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020088</v>
+        <v>127020066</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>80151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721480</v>
+        <v>721461</v>
       </c>
       <c r="R14" t="n">
-        <v>7215986</v>
+        <v>7216007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020040</v>
+        <v>127020103</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,42 +2432,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721589</v>
+        <v>721634</v>
       </c>
       <c r="R19" t="n">
-        <v>7215823</v>
+        <v>7215897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020103</v>
+        <v>127020040</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,34 +2529,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721634</v>
+        <v>721589</v>
       </c>
       <c r="R20" t="n">
-        <v>7215897</v>
+        <v>7215823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,6 +2597,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51644-2021 artfynd.xlsx
+++ b/artfynd/A 51644-2021 artfynd.xlsx
@@ -1742,32 +1742,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020088</v>
+        <v>127020075</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721480</v>
+        <v>721477</v>
       </c>
       <c r="R12" t="n">
-        <v>7215986</v>
+        <v>7215978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020075</v>
+        <v>127020066</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>80151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721477</v>
+        <v>721461</v>
       </c>
       <c r="R13" t="n">
-        <v>7215978</v>
+        <v>7216007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020066</v>
+        <v>127020088</v>
       </c>
       <c r="B14" t="n">
-        <v>80151</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721461</v>
+        <v>721480</v>
       </c>
       <c r="R14" t="n">
-        <v>7216007</v>
+        <v>7215986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020063</v>
+        <v>127020085</v>
       </c>
       <c r="B15" t="n">
-        <v>92634</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721474</v>
+        <v>721625</v>
       </c>
       <c r="R15" t="n">
-        <v>7215923</v>
+        <v>7215839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020085</v>
+        <v>127020063</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>92640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721625</v>
+        <v>721474</v>
       </c>
       <c r="R16" t="n">
-        <v>7215839</v>
+        <v>7215923</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
         <v>127020015</v>
       </c>
       <c r="B21" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,53 +2725,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020050</v>
+        <v>127020087</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721534</v>
+        <v>721498</v>
       </c>
       <c r="R22" t="n">
-        <v>7216097</v>
+        <v>7215896</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,11 +2796,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,45 +2822,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020087</v>
+        <v>127020050</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>56855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721498</v>
+        <v>721534</v>
       </c>
       <c r="R23" t="n">
-        <v>7215896</v>
+        <v>7216097</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,6 +2901,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,32 +2932,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020106</v>
+        <v>127020086</v>
       </c>
       <c r="B24" t="n">
-        <v>82861</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721632</v>
+        <v>721605</v>
       </c>
       <c r="R24" t="n">
-        <v>7215859</v>
+        <v>7215838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,32 +3029,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020086</v>
+        <v>127020106</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>82861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721605</v>
+        <v>721632</v>
       </c>
       <c r="R25" t="n">
-        <v>7215838</v>
+        <v>7215859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
